--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monsters" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_base" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_items" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="constants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="tiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="monsters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="boss" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="player_base" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="shop_items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -593,11 +593,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GEN_CHANCE_STAIRS</t>
+          <t>GEN_CHANCE_MERCHANT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -608,15 +608,77 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GEN_CHANCE_MERCHANT</t>
+          <t>CHUNK_SIZE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03</v>
+        <v>20</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ELITE_MIN_FLOOR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ELITE_CHANCE</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ELITE_STAT_MULT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NAME_STYLE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>fantasy</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>str</t>
         </is>
       </c>
     </row>

--- a/data/game_data.xlsx
+++ b/data/game_data.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="constants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="tiles" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="monsters" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="items" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="boss" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="player_base" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="shop_items" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="skills" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiles" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="monsters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="boss" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="player_base" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="shop_items" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skills" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -53,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +684,106 @@
         <is>
           <t>str</t>
         </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FLOOR_MONSTER_MULT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MONSTER_DEPTH_BIAS</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MAP_EXPORT_RADIUS</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MAP_EXPORT_PX</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>24</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BOSS_HP_MULT</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BOSS_ATK_MULT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BOSS_DEF_MULT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CAMERA_DEADZONE</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -791,43 +895,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>char</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>hp</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>attack</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>defense</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>exp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gold</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>min_floor</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>cr</t>
         </is>
       </c>
     </row>
@@ -839,50 +964,62 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Slime</t>
+          <t>史莱姆 Slime</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>r</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>巨鼠 Giant Rat</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="4">
@@ -893,50 +1030,1250 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Skeleton</t>
+          <t>狗头人 Kobold</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>哥布林 Goblin</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>44</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>巨蝙蝠 Giant Bat</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>怯魔 Dretch</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>44</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>闪现犬 Blink Dog</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>26</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>大地精 Hobgoblin</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>豺狼人 Gnoll</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>58</v>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>骷髅兵 Skeleton</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>58</v>
+      </c>
+      <c r="D11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>w</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>凶狼 Dire Wolf</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>85</v>
+      </c>
+      <c r="D12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>巨蜘蛛 Giant Spider</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>85</v>
+      </c>
+      <c r="D13" t="n">
+        <v>17</v>
+      </c>
+      <c r="E13" t="n">
+        <v>6</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>食尸鬼 Ghoul</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>21</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>o</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Orc</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>180</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>兽人 Orc</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>140</v>
+      </c>
+      <c r="D15" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>122</v>
+      </c>
+      <c r="G15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>q</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>妖鬼 Ghast</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>140</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>122</v>
+      </c>
+      <c r="G16" t="n">
+        <v>37</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>石像鬼 Gargoyle</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>140</v>
+      </c>
+      <c r="D17" t="n">
+        <v>26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>122</v>
+      </c>
+      <c r="G17" t="n">
+        <v>37</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>食人魔 Ogre</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>140</v>
+      </c>
+      <c r="D18" t="n">
+        <v>26</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>122</v>
+      </c>
+      <c r="G18" t="n">
+        <v>37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>木乃伊 Mummy</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>195</v>
+      </c>
+      <c r="D19" t="n">
         <v>35</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E19" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>177</v>
+      </c>
+      <c r="G19" t="n">
+        <v>53</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>牛头人 Minotaur</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>195</v>
+      </c>
+      <c r="D20" t="n">
+        <v>35</v>
+      </c>
+      <c r="E20" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" t="n">
+        <v>177</v>
+      </c>
+      <c r="G20" t="n">
+        <v>53</v>
+      </c>
+      <c r="H20" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>狼人 Werewolf, Wolf Form</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>195</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>14</v>
+      </c>
+      <c r="F21" t="n">
+        <v>177</v>
+      </c>
+      <c r="G21" t="n">
+        <v>53</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>石化蜥蜴 Basilisk</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>195</v>
+      </c>
+      <c r="D22" t="n">
+        <v>35</v>
+      </c>
+      <c r="E22" t="n">
+        <v>14</v>
+      </c>
+      <c r="F22" t="n">
+        <v>177</v>
+      </c>
+      <c r="G22" t="n">
+        <v>53</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>双头巨人 Ettin</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>250</v>
+      </c>
+      <c r="D23" t="n">
+        <v>44</v>
+      </c>
+      <c r="E23" t="n">
         <v>18</v>
       </c>
-      <c r="F5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F23" t="n">
+        <v>232</v>
+      </c>
+      <c r="G23" t="n">
+        <v>69</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>幽灵 Ghost</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>250</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44</v>
+      </c>
+      <c r="E24" t="n">
+        <v>18</v>
+      </c>
+      <c r="F24" t="n">
+        <v>232</v>
+      </c>
+      <c r="G24" t="n">
+        <v>69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>夜鬼婆 Night Hag</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>305</v>
+      </c>
+      <c r="D25" t="n">
+        <v>53</v>
+      </c>
+      <c r="E25" t="n">
+        <v>22</v>
+      </c>
+      <c r="F25" t="n">
+        <v>287</v>
+      </c>
+      <c r="G25" t="n">
+        <v>85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>山丘巨人 Hill Giant</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>305</v>
+      </c>
+      <c r="D26" t="n">
+        <v>53</v>
+      </c>
+      <c r="E26" t="n">
+        <v>22</v>
+      </c>
+      <c r="F26" t="n">
+        <v>287</v>
+      </c>
+      <c r="G26" t="n">
+        <v>85</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>肉魔像 Flesh Golem</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>305</v>
+      </c>
+      <c r="D27" t="n">
+        <v>53</v>
+      </c>
+      <c r="E27" t="n">
+        <v>22</v>
+      </c>
+      <c r="F27" t="n">
+        <v>287</v>
+      </c>
+      <c r="G27" t="n">
+        <v>85</v>
+      </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>双足飞龙 Wyvern</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>360</v>
+      </c>
+      <c r="D28" t="n">
+        <v>62</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26</v>
+      </c>
+      <c r="F28" t="n">
+        <v>342</v>
+      </c>
+      <c r="G28" t="n">
+        <v>101</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>奇美拉 Chimera</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>360</v>
+      </c>
+      <c r="D29" t="n">
+        <v>62</v>
+      </c>
+      <c r="E29" t="n">
+        <v>26</v>
+      </c>
+      <c r="F29" t="n">
+        <v>342</v>
+      </c>
+      <c r="G29" t="n">
+        <v>101</v>
+      </c>
+      <c r="H29" t="n">
+        <v>14</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>美杜莎 Medusa</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>360</v>
+      </c>
+      <c r="D30" t="n">
+        <v>62</v>
+      </c>
+      <c r="E30" t="n">
+        <v>26</v>
+      </c>
+      <c r="F30" t="n">
+        <v>342</v>
+      </c>
+      <c r="G30" t="n">
+        <v>101</v>
+      </c>
+      <c r="H30" t="n">
+        <v>14</v>
+      </c>
+      <c r="I30" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>多头蛇 Hydra</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>470</v>
+      </c>
+      <c r="D31" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" t="n">
+        <v>34</v>
+      </c>
+      <c r="F31" t="n">
+        <v>452</v>
+      </c>
+      <c r="G31" t="n">
+        <v>133</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>幼年绿龙 Young Green Dragon</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>470</v>
+      </c>
+      <c r="D32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" t="n">
+        <v>34</v>
+      </c>
+      <c r="F32" t="n">
+        <v>452</v>
+      </c>
+      <c r="G32" t="n">
+        <v>133</v>
+      </c>
+      <c r="H32" t="n">
+        <v>18</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>霜巨人 Frost Giant</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>470</v>
+      </c>
+      <c r="D33" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" t="n">
+        <v>34</v>
+      </c>
+      <c r="F33" t="n">
+        <v>452</v>
+      </c>
+      <c r="G33" t="n">
+        <v>133</v>
+      </c>
+      <c r="H33" t="n">
+        <v>18</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>幼年红龙 Young Red Dragon</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>580</v>
+      </c>
+      <c r="D34" t="n">
+        <v>98</v>
+      </c>
+      <c r="E34" t="n">
+        <v>42</v>
+      </c>
+      <c r="F34" t="n">
+        <v>562</v>
+      </c>
+      <c r="G34" t="n">
+        <v>165</v>
+      </c>
+      <c r="H34" t="n">
+        <v>23</v>
+      </c>
+      <c r="I34" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>底栖魔鱼 Aboleth</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>580</v>
+      </c>
+      <c r="D35" t="n">
+        <v>98</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42</v>
+      </c>
+      <c r="F35" t="n">
+        <v>562</v>
+      </c>
+      <c r="G35" t="n">
+        <v>165</v>
+      </c>
+      <c r="H35" t="n">
+        <v>23</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>石魔像 Stone Golem</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>580</v>
+      </c>
+      <c r="D36" t="n">
+        <v>98</v>
+      </c>
+      <c r="E36" t="n">
+        <v>42</v>
+      </c>
+      <c r="F36" t="n">
+        <v>562</v>
+      </c>
+      <c r="G36" t="n">
+        <v>165</v>
+      </c>
+      <c r="H36" t="n">
+        <v>23</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>六臂蛇魔 Marilith</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>910</v>
+      </c>
+      <c r="D37" t="n">
+        <v>152</v>
+      </c>
+      <c r="E37" t="n">
+        <v>66</v>
+      </c>
+      <c r="F37" t="n">
+        <v>892</v>
+      </c>
+      <c r="G37" t="n">
+        <v>261</v>
+      </c>
+      <c r="H37" t="n">
+        <v>36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>成年蓝龙 Adult Blue Dragon</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>910</v>
+      </c>
+      <c r="D38" t="n">
+        <v>152</v>
+      </c>
+      <c r="E38" t="n">
+        <v>66</v>
+      </c>
+      <c r="F38" t="n">
+        <v>892</v>
+      </c>
+      <c r="G38" t="n">
+        <v>261</v>
+      </c>
+      <c r="H38" t="n">
+        <v>36</v>
+      </c>
+      <c r="I38" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>铁魔像 Iron Golem</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>910</v>
+      </c>
+      <c r="D39" t="n">
+        <v>152</v>
+      </c>
+      <c r="E39" t="n">
+        <v>66</v>
+      </c>
+      <c r="F39" t="n">
+        <v>892</v>
+      </c>
+      <c r="G39" t="n">
+        <v>261</v>
+      </c>
+      <c r="H39" t="n">
+        <v>36</v>
+      </c>
+      <c r="I39" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>深狱炼魔 Pit Fiend</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D40" t="n">
+        <v>188</v>
+      </c>
+      <c r="E40" t="n">
+        <v>82</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1112</v>
+      </c>
+      <c r="G40" t="n">
+        <v>325</v>
+      </c>
+      <c r="H40" t="n">
         <v>45</v>
+      </c>
+      <c r="I40" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>远古白龙 Ancient White Dragon</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D41" t="n">
+        <v>188</v>
+      </c>
+      <c r="E41" t="n">
+        <v>82</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1112</v>
+      </c>
+      <c r="G41" t="n">
+        <v>325</v>
+      </c>
+      <c r="H41" t="n">
+        <v>45</v>
+      </c>
+      <c r="I41" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
